--- a/public/sap-reporting/expansion-150-downloads/EXT-PP07-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP07-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rb5968c270be646dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rb8c2cf1f15ee4be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rbef702f1fdca4c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R2d6172636edc42aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R37c160284ac14a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R91e91dccd68a4eab"/>
   </x:sheets>
 </x:workbook>
 </file>
